--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/o-higgins.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Productos Medicos Limitada</t>
+          <t>PRODUCTOS MEDICOS LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1424,6 +1424,311 @@
       </c>
       <c r="M16" s="2" t="n">
         <v>38027.02</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1622-1131-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.602.141-9</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BLUNDING S.A.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>79.744.580-0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>2476.89</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5326-1217-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.602.140-0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>GLOBALMED SpA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>38166.18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2080-9036-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.602.138-9</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>78.073.910-k</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>24443.23</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2080-9967-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.602.138-9</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>3521.22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1213444-440-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>71.328.600-1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>HEMISFERIO SUR S.A.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.533.330-4</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>4463.45</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/o-higgins.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/o-higgins.xlsx
@@ -867,7 +867,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +993,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1058,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1184,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1249,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1497,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/o-higgins.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1136,7 +1136,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5326-868-CM26</t>
+          <t>5326-869-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>17010.09</v>
+        <v>38503.97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5326-869-CM26</t>
+          <t>5326-868-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>38503.97</v>
+        <v>17010.09</v>
       </c>
     </row>
     <row r="14">
@@ -1449,7 +1449,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1622-1131-CM26</t>
+          <t>2107-1811-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1469,17 +1469,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1489,32 +1489,28 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BLUNDING S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>79.744.580-0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2476.89</v>
+        <v>2413.38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5326-1217-CM26</t>
+          <t>1622-1131-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1529,22 +1525,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1554,28 +1550,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>BLUNDING S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>79.744.580-0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>38166.18</v>
+        <v>2476.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2080-9036-CM26</t>
+          <t>5326-1217-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS LIMITADA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>78.073.910-k</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1630,13 +1630,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>24443.23</v>
+        <v>38166.18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2080-9967-CM26</t>
+          <t>2107-1901-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1691,13 +1691,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3521.22</v>
+        <v>7710.83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1213444-440-CM26</t>
+          <t>2080-9036-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>PRODUCTOS MEDICOS LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>78.073.910-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1752,7 +1752,190 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
+        <v>24443.23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1213444-440-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>71.328.600-1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>HEMISFERIO SUR S.A.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>96.533.330-4</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
         <v>4463.45</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2080-9967-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.602.138-9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>3521.22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2080-10034-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>61.602.138-9</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>TECNOMEDICAL S A</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>44144.01</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/o-higgins.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2107-1195-CM26</t>
+          <t>2080-5732-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OSTEOTRAUMA SPA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.965.562-K</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2586.41</v>
+        <v>6101.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2107-1196-CM26</t>
+          <t>2107-1195-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>OSTEOTRAUMA SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.965.562-K</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4965.9</v>
+        <v>2586.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2107-1197-CM26</t>
+          <t>2107-1196-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -859,32 +859,28 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>30573.74</v>
+        <v>4965.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5326-859-CM26</t>
+          <t>2107-1197-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -899,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -924,28 +920,32 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>14894.44</v>
+        <v>30573.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5326-864-CM26</t>
+          <t>5326-859-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -985,32 +985,28 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>46479.34</v>
+        <v>14894.44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5326-865-CM26</t>
+          <t>5326-864-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1030,7 +1026,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1069,13 +1065,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>29971.27</v>
+        <v>46479.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5326-867-CM26</t>
+          <t>5326-865-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1085,17 +1081,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1115,28 +1111,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>48316.94</v>
+        <v>29971.27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5326-869-CM26</t>
+          <t>5326-867-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1176,32 +1176,28 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>38503.97</v>
+        <v>48316.94</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5326-868-CM26</t>
+          <t>5326-869-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1221,7 +1217,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1260,13 +1256,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>17010.09</v>
+        <v>38503.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2107-1497-CM26</t>
+          <t>5326-868-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,22 +1277,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1306,28 +1302,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8882.17</v>
+        <v>17010.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2080-7285-CM26</t>
+          <t>2080-7102-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>78.073.910-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1382,13 +1382,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>25308.85</v>
+        <v>9406.209999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2080-8391-CM26</t>
+          <t>2107-1497-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1398,27 +1398,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS LIMITADA</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>78.073.910-k</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>38027.02</v>
+        <v>8882.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2107-1811-CM26</t>
+          <t>2080-7285-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1459,27 +1459,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>PRODUCTOS MEDICOS LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>78.073.910-k</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2413.38</v>
+        <v>25308.85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1622-1131-CM26</t>
+          <t>2080-8391-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1550,32 +1550,28 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>BLUNDING S.A.</t>
+          <t>PRODUCTOS MEDICOS LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>79.744.580-0</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.073.910-k</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2476.89</v>
+        <v>38027.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5326-1217-CM26</t>
+          <t>2107-1794-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1585,12 +1581,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1600,12 +1596,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1615,12 +1611,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1630,13 +1626,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>38166.18</v>
+        <v>41622.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2107-1901-CM26</t>
+          <t>2107-1811-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1651,7 +1647,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1691,13 +1687,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7710.83</v>
+        <v>2413.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2080-9036-CM26</t>
+          <t>1622-1131-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1712,22 +1708,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1737,28 +1733,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS LIMITADA</t>
+          <t>BLUNDING S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.073.910-k</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>79.744.580-0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>24443.23</v>
+        <v>2476.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1213444-440-CM26</t>
+          <t>5326-1217-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1798,12 +1798,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1813,13 +1813,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4463.45</v>
+        <v>38166.18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2080-9967-CM26</t>
+          <t>2107-1901-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1874,13 +1874,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3521.22</v>
+        <v>7710.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2080-10034-CM26</t>
+          <t>2080-9036-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>PRODUCTOS MEDICOS LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>78.073.910-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1935,6 +1935,189 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
+        <v>24443.23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1213444-440-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>71.328.600-1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>HEMISFERIO SUR S.A.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>96.533.330-4</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>4463.45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2080-9967-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.602.138-9</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>3521.22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2080-10034-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.602.138-9</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TECNOMEDICAL S A</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
         <v>44144.01</v>
       </c>
     </row>
